--- a/Excel/Sales Dataset .xlsx
+++ b/Excel/Sales Dataset .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANALYST\AI NIXA\Excel-PowerBI-training-resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DCD4643-B688-46A2-8245-AC6CDD4B5ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B71BBD7-184B-4842-AD9B-35B57177BBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{91339625-6693-4BB6-86E0-44F33A55F6BC}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Additional" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
